--- a/out/LSTM-mamba2_repeat_3_000001.xlsx
+++ b/out/LSTM-mamba2_repeat_3_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.9612393007297437</v>
+        <v>5.934848009080797</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.01436208449146875</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.854026995542006</v>
+        <v>6.534848009080797</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.854026995542006</v>
+        <v>6.534848009080797</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.854026995542006</v>
+        <v>6.534848009080797</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.854026995542006</v>
+        <v>6.534848009080797</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.561239300729744</v>
+        <v>6.534848009080797</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.01436208449146875</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002275148730685469</v>
+        <v>-4.982173899491318e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.09796129869639654</v>
+        <v>0.02145168721587426</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.1961840301988907</v>
+        <v>0.04296083828415477</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3784754766391459</v>
+        <v>0.0828800398869721</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8554258532732805</v>
+        <v>0.1873238746955791</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1164211782386261</v>
+        <v>0.0254943648708457</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.7093129774083167</v>
+        <v>0.1553276454136902</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.0236227230808632</v>
+        <v>0.005171214936042325</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.6399545097053225</v>
+        <v>0.1401378155024282</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02045832805004406</v>
+        <v>0.004477505261101273</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.6572226303880114</v>
+        <v>0.1439166224496483</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01000161227476908</v>
+        <v>0.002186055487693608</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.6567411215512012</v>
+        <v>0.1438073056341743</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.004771090676194267</v>
+        <v>0.001040688571382768</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.6562702929723552</v>
+        <v>0.1437002841406898</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001984682265667356</v>
+        <v>0.000430904088980845</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.6554630834608816</v>
+        <v>0.1435195342673031</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.00137397695267668</v>
+        <v>0.0002967235526002137</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.6562245535440834</v>
+        <v>0.1436824550282816</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005703483121322848</v>
+        <v>0.000121280256638217</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.6559904191477429</v>
+        <v>0.1436271914847982</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002936727101649184</v>
+        <v>6.048081788850562e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.656006171678432</v>
+        <v>0.1436267412566272</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001120446912784018</v>
+        <v>2.071834023606139e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.6559367623754009</v>
+        <v>0.1436076200667473</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>5.913492526961955e-05</v>
+        <v>8.743198272061334e-06</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.6559423315458929</v>
+        <v>0.1436049327155624</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.662161700254366e-05</v>
+        <v>1.776060786259356e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.6559363673287391</v>
+        <v>0.1435997181265063</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>9.919117236739567e-06</v>
+        <v>-1.80304630641295e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.6559295471476077</v>
+        <v>0.1435942962033146</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.456405945771008e-06</v>
+        <v>-3.616484440191926e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.6559225223090469</v>
+        <v>0.1435887905694873</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.106181251314092e-06</v>
+        <v>-4.173194643232597e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6559168450774772</v>
+        <v>0.1435835970747531</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.04640701416283e-06</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.6559111725671929</v>
+        <v>0.1435784047890361</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.6559056288990904</v>
+        <v>0.1435782692804304</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.777674021158921e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.655900707745369</v>
+        <v>0.1435783091359027</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.6559007476008414</v>
+        <v>0.1435783489913749</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.6559007396297469</v>
+        <v>0.1435783410202805</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.655900899051636</v>
+        <v>0.1435785004421696</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.6559008033985025</v>
+        <v>0.1435784047890361</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6559011541266588</v>
+        <v>0.1435787555171924</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6559009070227304</v>
+        <v>0.1435785084132641</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6559008671672582</v>
+        <v>0.1435784685577918</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.6559008033985025</v>
+        <v>0.1435784047890361</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6559008751383526</v>
+        <v>0.1435784765288863</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.6559008033985025</v>
+        <v>0.1435784047890361</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6559009070227304</v>
+        <v>0.1435785084132641</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6559010026758642</v>
+        <v>0.1435786040663978</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6559009389071083</v>
+        <v>0.1435785402976419</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.655900899051636</v>
+        <v>0.1435785004421696</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6559008751383526</v>
+        <v>0.1435784765288863</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6559006280344245</v>
+        <v>0.1435782294249581</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6559005483234797</v>
+        <v>0.1435781497140133</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.6559005961500465</v>
+        <v>0.1435781975405801</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6559007157164635</v>
+        <v>0.1435783171069971</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6559006997742746</v>
+        <v>0.1435783011648082</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6559007157164635</v>
+        <v>0.1435783171069971</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6559006997742746</v>
+        <v>0.1435783011648082</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6559007555719358</v>
+        <v>0.1435783569624694</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6559007555719358</v>
+        <v>0.1435783569624694</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6559007555719358</v>
+        <v>0.1435783569624694</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6559009070227304</v>
+        <v>0.1435785084132641</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.655901122242281</v>
+        <v>0.1435787236328146</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.655901034560242</v>
+        <v>0.1435786359507756</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6559009867336753</v>
+        <v>0.1435785881242088</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.655901034560242</v>
+        <v>0.1435786359507756</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6559008512250692</v>
+        <v>0.1435784526156029</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6559008591961637</v>
+        <v>0.1435784605866973</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6559008671672582</v>
+        <v>0.1435784685577918</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6559008751383526</v>
+        <v>0.1435784765288863</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6559008751383526</v>
+        <v>0.1435784765288863</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.6559009149938249</v>
+        <v>0.1435785163843585</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6559009787625808</v>
+        <v>0.1435785801531144</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6559010903579031</v>
+        <v>0.1435786917484368</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6559011381844699</v>
+        <v>0.1435787395750035</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6559010983289976</v>
+        <v>0.1435786997195312</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.6559010265891475</v>
+        <v>0.1435786279796811</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6559011461555644</v>
+        <v>0.143578747546098</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6559009867336753</v>
+        <v>0.1435785881242088</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6559007555719358</v>
+        <v>0.1435783569624694</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.655900707745369</v>
+        <v>0.1435783091359027</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.6559007396297469</v>
+        <v>0.1435783410202805</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.6559008033985025</v>
+        <v>0.1435784047890361</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.6559008033985025</v>
+        <v>0.1435784047890361</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6559007236875579</v>
+        <v>0.1435783250780916</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6559006041211409</v>
+        <v>0.1435782055116745</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6559005642656687</v>
+        <v>0.1435781656562022</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.655900707745369</v>
+        <v>0.1435783091359027</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6559008432539748</v>
+        <v>0.1435784446445084</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6559008273117859</v>
+        <v>0.1435784287023195</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.6559008033985025</v>
+        <v>0.1435784047890361</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6559007635430303</v>
+        <v>0.1435783649335639</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.6559006599188023</v>
+        <v>0.1435782613093359</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6559005403523852</v>
+        <v>0.1435781417429189</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6559006599188023</v>
+        <v>0.1435782613093359</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.561239300729744</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.655900707745369</v>
+        <v>0.1435783091359027</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.6559008033985025</v>
+        <v>0.1435784047890361</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6559006838320857</v>
+        <v>0.1435782852226193</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.6559006918031801</v>
+        <v>0.1435782931937138</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_3_000001.xlsx
+++ b/out/LSTM-mamba2_repeat_3_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.2621290720809756</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.2621290720809756</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.2621290720809756</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.2621290720809756</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002275148730685469</v>
+        <v>-0.0001837050263792044</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.09796129869639654</v>
+        <v>0.07909805068326831</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.1961840301988907</v>
+        <v>0.1584071931509674</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3784754766391459</v>
+        <v>0.305596773674205</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8554258532732805</v>
+        <v>0.690706620153961</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1164211782386261</v>
+        <v>0.0940032806696091</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.7093129774083167</v>
+        <v>0.5727289104039387</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.0236227230808632</v>
+        <v>0.01907417146980507</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.6399545097053225</v>
+        <v>0.5167258938961655</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02045832805004406</v>
+        <v>0.01651908020410168</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.9612393007297437</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.6572226303880114</v>
+        <v>0.5306687960814289</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01000161227476908</v>
+        <v>0.008074604613086142</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.6567411215512012</v>
+        <v>0.5302791665036306</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.004771090676194267</v>
+        <v>0.003851018367699652</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.6562702929723552</v>
+        <v>0.5298980438626048</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001984682265667356</v>
+        <v>0.001601665645975375</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.6554630834608816</v>
+        <v>0.5292452608043752</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.00137397695267668</v>
+        <v>0.001108521960107694</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.6562245535440834</v>
+        <v>0.5298591843242746</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005703483121322848</v>
+        <v>0.0004595309440620126</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.6559904191477429</v>
+        <v>0.5296691587518072</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002936727101649184</v>
+        <v>0.0002362099516096993</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.656006171678432</v>
+        <v>0.5296809186255851</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001120446912784018</v>
+        <v>8.947553556104185e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.6559367623754009</v>
+        <v>0.5296239013871424</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>5.913492526961955e-05</v>
+        <v>4.653699352023e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.6559423315458929</v>
+        <v>0.5296274422971401</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.662161700254366e-05</v>
+        <v>2.041022794847258e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.6559363673287391</v>
+        <v>0.52962165950869</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>9.919117236739567e-06</v>
+        <v>7.254989158750358e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.6559295471476077</v>
+        <v>0.5296151643599036</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.456405945771008e-06</v>
+        <v>7.289038596293463e-08</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.6559225223090469</v>
+        <v>0.52960850167547</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.106181251314092e-06</v>
+        <v>-2.519583929697793e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6559168450774772</v>
+        <v>0.5296029211912674</v>
       </c>
     </row>
     <row r="61">
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.6559111725671929</v>
+        <v>0.5295973443341166</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.6559056288990904</v>
+        <v>0.5295919369914597</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.655900707745369</v>
+        <v>0.5295870158377383</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.6559007476008414</v>
+        <v>0.5295870556932105</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.6559007396297469</v>
+        <v>0.5295870477221161</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.655900899051636</v>
+        <v>0.5295872071440052</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.6559008033985025</v>
+        <v>0.5295871114908718</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.9612393007297437</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6559011541266588</v>
+        <v>0.5295874622190281</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6559009070227304</v>
+        <v>0.5295872151150997</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6559008671672582</v>
+        <v>0.5295871752596274</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.6559008033985025</v>
+        <v>0.5295871114908718</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6559008751383526</v>
+        <v>0.5295871832307218</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.6559008033985025</v>
+        <v>0.5295871114908718</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6559009070227304</v>
+        <v>0.5295872151150997</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.8248498062146816</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6559010026758642</v>
+        <v>0.5295873107682334</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6559009389071083</v>
+        <v>0.5295872469994775</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.2621290720809756</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.655900899051636</v>
+        <v>0.5295872071440052</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6559008751383526</v>
+        <v>0.5295871832307218</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6559006280344245</v>
+        <v>0.5295869361267938</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6559005483234797</v>
+        <v>0.5295868564158489</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.6559005961500465</v>
+        <v>0.5295869042424157</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6559007157164635</v>
+        <v>0.5295870238088327</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6559006997742746</v>
+        <v>0.5295870078666438</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6559007157164635</v>
+        <v>0.5295870238088327</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6559006997742746</v>
+        <v>0.5295870078666438</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6559007555719358</v>
+        <v>0.529587063664305</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.254026995542006</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6559007555719358</v>
+        <v>0.529587063664305</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6559007555719358</v>
+        <v>0.529587063664305</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6559009070227304</v>
+        <v>0.5295872151150997</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.655901122242281</v>
+        <v>0.5295874303346502</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.655901034560242</v>
+        <v>0.5295873426526112</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.854026995542006</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6559009867336753</v>
+        <v>0.5295872948260445</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.655901034560242</v>
+        <v>0.5295873426526112</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6559008512250692</v>
+        <v>0.5295871593174385</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6559008591961637</v>
+        <v>0.5295871672885329</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6559008671672582</v>
+        <v>0.5295871752596274</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6559008751383526</v>
+        <v>0.5295871832307218</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6559008751383526</v>
+        <v>0.5295871832307218</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.9612393007297437</v>
+        <v>0.181360367066853</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.6559009149938249</v>
+        <v>0.5295872230861941</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6559009787625808</v>
+        <v>0.52958728685495</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6559010903579031</v>
+        <v>0.5295873984502724</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6559011381844699</v>
+        <v>0.5295874462768391</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6559010983289976</v>
+        <v>0.5295874064213668</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.6559010265891475</v>
+        <v>0.5295873346815168</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6559011461555644</v>
+        <v>0.5295874542479336</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6559009867336753</v>
+        <v>0.5295872948260445</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6559007555719358</v>
+        <v>0.529587063664305</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.655900707745369</v>
+        <v>0.5295870158377383</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.6559007396297469</v>
+        <v>0.5295870477221161</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.6559008033985025</v>
+        <v>0.5295871114908718</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.6559008033985025</v>
+        <v>0.5295871114908718</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6559007236875579</v>
+        <v>0.5295870317799272</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.854026995542006</v>
+        <v>-1.105618511228804</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6559006041211409</v>
+        <v>0.5295869122135102</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6559005642656687</v>
+        <v>0.5295868723580378</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.655900707745369</v>
+        <v>0.5295870158377383</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6559008432539748</v>
+        <v>0.529587151346344</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.2621290720809756</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6559008273117859</v>
+        <v>0.5295871354041551</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.9056185112288041</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.6559008033985025</v>
+        <v>0.5295871114908718</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6559007635430303</v>
+        <v>0.5295870716353995</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.6559006599188023</v>
+        <v>0.5295869680111716</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6559005403523852</v>
+        <v>0.5295868484447545</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.561239300729744</v>
+        <v>1.024849806214682</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6559006599188023</v>
+        <v>0.5295869680111716</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.561239300729744</v>
+        <v>0.381360367066853</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.655900707745369</v>
+        <v>0.5295870158377383</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.254026995542006</v>
+        <v>-0.2621290720809756</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.6559008033985025</v>
+        <v>0.5295871114908718</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.854026995542006</v>
+        <v>-0.4621290720809756</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6559006838320857</v>
+        <v>0.5295869919244549</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.9612393007297437</v>
+        <v>-0.1403843525070613</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.6559006918031801</v>
+        <v>0.5295869998955494</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_3_000001.xlsx
+++ b/out/LSTM-mamba2_repeat_3_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.239216074347496</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.1537226587533951</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.3700000000000002</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.04567930847406387</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.381360367066853</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.01775459572672844</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.2621290720809756</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.03087798878550529</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.008465539664030075</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.02665288746356964</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.03440939635038376</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.02057366073131561</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.02885009348392487</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.01977010816335678</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.02303063496947289</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.00711425393819809</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.2621290720809756</v>
+        <v>0.16</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.02080441266298294</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.381360367066853</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.03663246333599091</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.024849806214682</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.03820616006851196</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.024849806214682</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.01170359551906586</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.024849806214682</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.001082930713891983</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.381360367066853</v>
+        <v>0.16</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.001251079142093658</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.2621290720809756</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.01282490789890289</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.0174948126077652</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.007979832589626312</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.006219238042831421</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.181360367066853</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.01356169581413269</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.024849806214682</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>4.170835018157959e-05</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.381360367066853</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.009120691567659378</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.2621290720809756</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.01359205693006516</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.0225025974214077</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.01170940697193146</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.02131809294223785</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.4621290720809756</v>
+        <v>0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.0001095905900001526</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.4621290720809756</v>
+        <v>0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.002329092472791672</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.105618511228804</v>
+        <v>0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.02073803916573524</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.105618511228804</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.02758380770683289</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.02975735068321228</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.01579033583402634</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.001907333731651306</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.4621290720809756</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.008732564747333527</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.381360367066853</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.04242639243602753</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.024849806214682</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.065947525203228</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.024849806214682</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.09066851437091827</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.024849806214682</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.09292183816432953</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.024849806214682</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0001837050263792044</v>
+        <v>-0.0001816752822221024</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.07909805068326831</v>
+        <v>0.07822410178061202</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.08256538212299347</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.024849806214682</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.1584071931509674</v>
+        <v>0.1566569630070983</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.305596773674205</v>
+        <v>0.3022210742498265</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.05824092030525208</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.024849806214682</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.690706620153961</v>
+        <v>0.6830750487817598</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.0940032806696091</v>
+        <v>0.09296489660347235</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.03540815412998199</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.024849806214682</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.5727289104039387</v>
+        <v>0.5664011813620098</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.01907417146980507</v>
+        <v>0.01886306248949166</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.02975153177976608</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.024849806214682</v>
+        <v>-0.16</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.5167258938961655</v>
+        <v>0.5110173888417329</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01651908020410168</v>
+        <v>0.01633660823303623</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.01672719419002533</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.024849806214682</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.5306687960814289</v>
+        <v>0.5248062758631562</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.008074604613086142</v>
+        <v>0.007985702361668543</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.02031576633453369</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.3</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.5302791665036306</v>
+        <v>0.524420894243811</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.003851018367699652</v>
+        <v>0.003808255384588791</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.01965022832155228</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.3</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.5298980438626048</v>
+        <v>0.5240439424238605</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001601665645975375</v>
+        <v>0.001583850919478074</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.02054807543754578</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.16</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.5292452608043752</v>
+        <v>0.5233983419913631</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001108521960107694</v>
+        <v>0.001096175216267276</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.01730434596538544</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.5298591843242746</v>
+        <v>0.5240054028804111</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0004595309440620126</v>
+        <v>0.0004543766478726977</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.0395541712641716</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.8248498062146816</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.5296691587518072</v>
+        <v>0.5238174288811471</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002362099516096993</v>
+        <v>0.0002335372651652704</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.04672926664352417</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.8248498062146816</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.5296809186255851</v>
+        <v>0.5238290030499527</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>8.947553556104185e-05</v>
+        <v>8.842580738814138e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.02140552550554276</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.8248498062146816</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.5296239013871424</v>
+        <v>0.5237725621866074</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>4.653699352023e-05</v>
+        <v>4.596436025889411e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.00761035829782486</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.181360367066853</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5296274422971401</v>
+        <v>0.5237760087290115</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.01238122582435608</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.52962165950869</v>
+        <v>0.5237702339116556</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.254989158750358e-06</v>
+        <v>6.722163543152517e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.009275011718273163</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5296151643599036</v>
+        <v>0.5237637718849604</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.0003311894834041595</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.181360367066853</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.52960850167547</v>
+        <v>0.5237571092005268</v>
       </c>
     </row>
     <row r="60">
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.007922869175672531</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.8248498062146816</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5296029211912674</v>
+        <v>0.5237515287163241</v>
       </c>
     </row>
     <row r="61">
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.01971249282360077</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.024849806214682</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5295973443341166</v>
+        <v>0.5237459518591734</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.0151989609003067</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.024849806214682</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5295919369914597</v>
+        <v>0.5237405445165164</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.02190018445253372</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.024849806214682</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5295870158377383</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.008476145565509796</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.024849806214682</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5295870556932105</v>
+        <v>0.5237356632182673</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.0206943154335022</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.024849806214682</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5295870477221161</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.01732498407363892</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.024849806214682</v>
+        <v>0.16</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5295872071440052</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.03928991407155991</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.024849806214682</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5295871114908718</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.0323379710316658</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.024849806214682</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5295874622190281</v>
+        <v>0.5237360697440847</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.01281647384166718</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.8248498062146816</v>
+        <v>0.16</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5295872151150997</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.01246489584445953</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.181360367066853</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5295871752596274</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.003851577639579773</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5295871114908718</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.006870739161968231</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5295871832307218</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.001824021339416504</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5295871114908718</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.06295207142829895</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.181360367066853</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5295872151150997</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.0464044064283371</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.8248498062146816</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5295873107682334</v>
+        <v>0.52373591829329</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.00286141037940979</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.381360367066853</v>
+        <v>0.16</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5295872469994775</v>
+        <v>0.5237358545245342</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.02508198097348213</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.2621290720809756</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5295872071440052</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.004699647426605225</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5295871832307218</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.004023127257823944</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5295869361267938</v>
+        <v>0.5237355436518504</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.01311670988798141</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5295868564158489</v>
+        <v>0.5237354639409056</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.01032229512929916</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5295869042424157</v>
+        <v>0.5237355117674724</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.01267195492982864</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5295870238088327</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-3.04877758026123e-05</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5295870078666438</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.0034751296043396</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.381360367066853</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5295870238088327</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.008574165403842926</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.024849806214682</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5295870078666438</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.00577453151345253</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.381360367066853</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.529587063664305</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.01004655659198761</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.381360367066853</v>
+        <v>0.16</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.529587063664305</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.02373275905847549</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.381360367066853</v>
+        <v>0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.529587063664305</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.008971363306045532</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.024849806214682</v>
+        <v>0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5295872151150997</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.03725787252187729</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.024849806214682</v>
+        <v>0.3</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5295874303346502</v>
+        <v>0.5237360378597069</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.006465893238782883</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.381360367066853</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5295873426526112</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.008133061230182648</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.381360367066853</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5295872948260445</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.0004733726382255554</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5295873426526112</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.01107226312160492</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5295871593174385</v>
+        <v>0.5237357668424952</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.01591366901993752</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5295871672885329</v>
+        <v>0.5237357748135897</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.005256157368421555</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5295871752596274</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.01225005090236664</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5295871832307218</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.01329535618424416</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5295871832307218</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.02353058755397797</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.181360367066853</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5295872230861941</v>
+        <v>0.5237358306112508</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.02507416903972626</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.024849806214682</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.52958728685495</v>
+        <v>0.5237358943800067</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.0228104442358017</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.024849806214682</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5295873984502724</v>
+        <v>0.5237360059753291</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.003067780286073685</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.024849806214682</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5295874462768391</v>
+        <v>0.5237360538018958</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.004849161952733994</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.024849806214682</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5295874064213668</v>
+        <v>0.5237360139464236</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.0102001428604126</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.024849806214682</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5295873346815168</v>
+        <v>0.5237359422065735</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.01485098898410797</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.024849806214682</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5295874542479336</v>
+        <v>0.5237360617729903</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.02586758136749268</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.024849806214682</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5295872948260445</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.00658736377954483</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.381360367066853</v>
+        <v>-0.3</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.529587063664305</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.00382581353187561</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5295870158377383</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.01676299422979355</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5295870477221161</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.006418041884899139</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5295871114908718</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.01093258708715439</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5295871114908718</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.01054561510682106</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5295870317799272</v>
+        <v>0.5237356393049839</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.003887750208377838</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.105618511228804</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5295869122135102</v>
+        <v>0.5237355197385668</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.003057520836591721</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5295868723580378</v>
+        <v>0.5237354798830945</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.005275443196296692</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.381360367066853</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5295870158377383</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.002075280994176865</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.381360367066853</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.529587151346344</v>
+        <v>0.5237357588714008</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.009038977324962616</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.2621290720809756</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5295871354041551</v>
+        <v>0.5237357429292118</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.007594451308250427</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9056185112288041</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5295871114908718</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.003909479826688766</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.4621290720809756</v>
+        <v>0.16</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5295870716353995</v>
+        <v>0.5237356791604562</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.01337102055549622</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.381360367066853</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5295869680111716</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.02563074231147766</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.024849806214682</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5295868484447545</v>
+        <v>0.5237354559698112</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.005147732794284821</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.024849806214682</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5295869680111716</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.002101380378007889</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.381360367066853</v>
+        <v>0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5295870158377383</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.009546112269163132</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.2621290720809756</v>
+        <v>0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5295871114908718</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.008960463106632233</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.4621290720809756</v>
+        <v>-0.6500000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5295869919244549</v>
+        <v>0.5237355994495116</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.01049301773309708</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.1403843525070613</v>
+        <v>-0.8600000000000003</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5295869998955494</v>
+        <v>0.5237356074206061</v>
       </c>
     </row>
   </sheetData>
